--- a/output/pdf_financials_xlsx/DTEA.xlsx
+++ b/output/pdf_financials_xlsx/DTEA.xlsx
@@ -1999,40 +1999,40 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>19.784</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>72.514</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>64.44</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>63.484</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>42.074</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>46.338</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>30.197</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>25.107</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>22.44</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>16.187</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>16.478</v>
       </c>
     </row>
     <row r="35">
@@ -2095,40 +2095,40 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>19.784</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>72.514</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>64.44</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>63.484</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>42.074</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>46.338</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>30.197</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>25.107</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>22.44</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>16.187</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>16.478</v>
       </c>
     </row>
     <row r="37">
@@ -2671,40 +2671,40 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>38.558</v>
+        <v>18.774</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>101.523</v>
+        <v>29.009</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>105.841</v>
+        <v>41.401</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>77.295</v>
+        <v>13.811</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>58.681</v>
+        <v>16.607</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>80.501</v>
+        <v>34.163</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>74.34699999999999</v>
+        <v>44.15</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>29.249</v>
+        <v>4.142</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>28.279</v>
+        <v>5.839</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>17.57</v>
+        <v>4.97</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>18.065</v>
+        <v>1.878</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>18.168</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="49">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/DTEA.xlsx
+++ b/output/pdf_financials_xlsx/DTEA.xlsx
@@ -1757,37 +1757,37 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.944</v>
+        <v>4.745</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.573</v>
+        <v>5.447</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.613</v>
+        <v>6.445</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.758</v>
+        <v>8.827</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.474</v>
+        <v>9.904999999999999</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.298</v>
+        <v>8.202</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1.934</v>
+        <v>7.345</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.053</v>
+        <v>4.452</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.695</v>
+        <v>3.281</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.555</v>
+        <v>0.875</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.606</v>
+        <v>0.964</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>3.363</v>
@@ -1803,37 +1803,37 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.108</v>
+        <v>1.693</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>6.827</v>
+        <v>11.701</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-125.802</v>
+        <v>-119.97</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.666</v>
+        <v>3.403</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-24.45</v>
+        <v>-16.019</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-26.659</v>
+        <v>-19.755</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-29.979</v>
+        <v>-24.568</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-53.48</v>
+        <v>-51.081</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>78.965</v>
+        <v>80.551</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-13.899</v>
+        <v>-13.579</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-12.45</v>
+        <v>-12.092</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>0.554</v>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-1.948802337083638</v>
+        <v>1.565143432961384</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4.811711057702473</v>
+        <v>8.246935855599331</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-69.62311140627594</v>
+        <v>-66.39548397808402</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-2.160345210756352</v>
+        <v>1.575579672568338</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-10.91444769323483</v>
+        <v>-7.150860433453117</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-12.53049310703022</v>
+        <v>-9.285415481802842</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-15.25943948448046</v>
+        <v>-12.50521729392961</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-43.94918067813882</v>
+        <v>-41.97771313051625</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>75.87462646411653</v>
+        <v>77.39855678225861</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-16.74053910823116</v>
+        <v>-16.35511767398165</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-20.52998697293999</v>
+        <v>-19.93964678528437</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>0.8964256241808385</v>
@@ -5167,43 +5167,43 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>4.745</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>5.447</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>6.445</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>8.827</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>9.904999999999999</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>8.202</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>7.345</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>4.452</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>3.281</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.964</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="101">
@@ -5722,22 +5722,22 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.297</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.356</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>1.875</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -13142,7 +13142,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -16786,7 +16790,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -16863,7 +16871,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -17809,7 +17817,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -22089,7 +22101,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E196" s="5" t="n">
         <v>3.801</v>
       </c>
@@ -22156,7 +22172,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
@@ -23277,7 +23293,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E212" s="5" t="n">
         <v>-0.442</v>
       </c>
@@ -26648,7 +26668,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DTEA.xlsx
+++ b/output/pdf_financials_xlsx/DTEA.xlsx
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>42.054</v>
+        <v>44.236</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>42.864</v>
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>42.054</v>
+        <v>44.236</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>42.864</v>
@@ -887,7 +887,7 @@
         <v>49.733</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.279</v>
+        <v>-1.903</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>-14.552</v>
@@ -1151,10 +1151,10 @@
         <v>2.235</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-2.01</v>
+        <v>-0.183</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-4.882</v>
+        <v>0.063</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>1.5</v>
@@ -1907,10 +1907,10 @@
         <v>-37.86210401490767</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-7.587482541240422</v>
+        <v>-0.6908006492771129</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-17.03597724814182</v>
+        <v>-0.2198415744844192</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-4.587576841912102</v>
@@ -2155,25 +2155,25 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>2.072</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>1.232</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>2.391</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>1.743</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0</v>
+        <v>1.069</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>0</v>
@@ -2287,40 +2287,40 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>1.948</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>1.115</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>4.274</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.384</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.725</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="41">
@@ -2335,25 +2335,25 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>1.948</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>2.204</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>3.187</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>5.506</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>3.209</v>
@@ -2671,25 +2671,25 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>18.774</v>
+        <v>18.215</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>29.009</v>
+        <v>27.919</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>41.401</v>
+        <v>39.453</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.811</v>
+        <v>11.971</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>16.607</v>
+        <v>14.403</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>34.163</v>
+        <v>30.976</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>44.15</v>
+        <v>38.644</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>4.142</v>
@@ -13077,7 +13077,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>-6.164</v>
       </c>
@@ -28882,7 +28886,11 @@
           <t>Deferred income taxes (recovered)</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E283" s="5" t="n">
         <v>0.102</v>
       </c>
@@ -37709,7 +37717,11 @@
           <t>Income tax recovery 20</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -45908,7 +45920,11 @@
           <t>Wages, salaries, bonus and director fees</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
           <t>-</t>
@@ -47961,7 +47977,11 @@
           <t>Provision for income tax recovery</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E524" t="inlineStr">
         <is>
           <t>-</t>
@@ -48713,7 +48733,11 @@
           <t>Provision for income tax recovery</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
